--- a/output/pdf_financials_xlsx/DAU.xlsx
+++ b/output/pdf_financials_xlsx/DAU.xlsx
@@ -1180,13 +1180,13 @@
         <v>-1.076701</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>14.630615</v>
+        <v>-14.630615</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.772068</v>
+        <v>-2.772068</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.963686</v>
+        <v>-1.963686</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-1.457612</v>
@@ -1448,13 +1448,13 @@
         <v>-1.076701</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>14.630615</v>
+        <v>-14.630615</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.772068</v>
+        <v>-2.772068</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.963686</v>
+        <v>-1.963686</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-1.457612</v>
@@ -1604,13 +1604,13 @@
         <v>-1.076701</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>14.630615</v>
+        <v>-14.630615</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.772068</v>
+        <v>-2.772068</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.963686</v>
+        <v>-1.963686</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-1.457612</v>
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-22.167598</v>
+        <v>22.167598</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46.201133</v>
+        <v>-46.201133</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>49.09215</v>
+        <v>-49.09215</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>4.417006</v>
@@ -1824,13 +1824,13 @@
         <v>-1.076701</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>14.630615</v>
+        <v>-14.630615</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.772068</v>
+        <v>-2.772068</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.963686</v>
+        <v>-1.963686</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.457612</v>
@@ -1928,13 +1928,13 @@
         <v>-1.076701</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>14.783618</v>
+        <v>-14.477612</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.808485</v>
+        <v>-2.735651</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.963686</v>
+        <v>-1.963686</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.442583</v>
@@ -2062,13 +2062,13 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5353,46 +5353,46 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>14.646931</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>16.80056</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>16.806863</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>16.806863</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>16.806863</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>16.916508</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>17.360803</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>17.499477</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>18.110865</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>18.936524</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>19.384426</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>19.488581</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>19.610497</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>19.785485</v>
       </c>
     </row>
     <row r="93">
@@ -8997,7 +8997,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -9798,7 +9802,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -10421,7 +10429,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11912,7 +11924,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -13002,7 +13018,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13983,7 +14003,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15803,7 +15827,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -33159,13 +33187,13 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>2.772068</v>
+        <v>-2.772068</v>
       </c>
       <c r="H286" s="5" t="n">
-        <v>1.963686</v>
+        <v>-1.963686</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>1.457612</v>
+        <v>-1.457612</v>
       </c>
       <c r="J286" s="5" t="n">
         <v>-0.735186</v>
@@ -44297,10 +44325,10 @@
         </is>
       </c>
       <c r="F411" s="5" t="n">
-        <v>14.630615</v>
+        <v>-14.630615</v>
       </c>
       <c r="G411" s="5" t="n">
-        <v>2.772068</v>
+        <v>-2.772068</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DAU.xlsx
+++ b/output/pdf_financials_xlsx/DAU.xlsx
@@ -2206,43 +2206,43 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.838577</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.381149</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.298717</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.317634</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.1517</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.290011</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.112331</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.204379</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.216664</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.220393</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.279575</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.348601</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.445077</v>
       </c>
     </row>
     <row r="35">
@@ -2310,43 +2310,43 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.838577</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.381149</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.298717</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.317634</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.1517</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.290011</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.112331</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.204379</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.096941</v>
+        <v>1.313605</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.055845</v>
+        <v>1.276238</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.279575</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.348601</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.445077</v>
       </c>
     </row>
     <row r="37">
@@ -2934,43 +2934,43 @@
         <v>3.837929</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.850151</v>
+        <v>0.011574</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.391903</v>
+        <v>0.010754</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.306154</v>
+        <v>0.007437</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.31808</v>
+        <v>0.000446</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.1517</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.292819</v>
+        <v>0.002808</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.112331</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.210595</v>
+        <v>0.006216</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.216664</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.229423</v>
+        <v>0.00903</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.28698</v>
+        <v>0.007405</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.352915</v>
+        <v>0.004314</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.449643</v>
+        <v>0.004566</v>
       </c>
     </row>
     <row r="49">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/DAU.xlsx
+++ b/output/pdf_financials_xlsx/DAU.xlsx
@@ -3813,43 +3813,43 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.833919</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.361119</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.178051</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.103464</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.033205</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.121191</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.318334</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.316985</v>
       </c>
       <c r="K64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.331669</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.391665</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.039642</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.07443900000000001</v>
       </c>
       <c r="P64" s="3" t="n">
         <v>0</v>
@@ -3969,46 +3969,46 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.199906</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.155529</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.141793</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.124657</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.168747</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.196027</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.01993</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.017519</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.033915</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.145268</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.148033</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.08447200000000001</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.100951</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.138122</v>
       </c>
     </row>
     <row r="68">
@@ -5838,19 +5838,19 @@
         <v>0.011867</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002654</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.003704</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008389000000000001</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002273</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010968</v>
       </c>
       <c r="L101" s="3" t="n">
         <v>-0.031788</v>
@@ -6104,13 +6104,13 @@
         <v>-0.408953</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.001199</v>
+        <v>-0.00719</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.150119</v>
+        <v>0.147846</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.039039</v>
+        <v>-0.050007</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0.011772</v>
@@ -6346,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>0.026739</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019559</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.234126</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -6385,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015287</v>
       </c>
     </row>
     <row r="112">
@@ -7578,10 +7578,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.026739</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019559</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -7596,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.234126</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -7617,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015287</v>
       </c>
     </row>
     <row r="135">
@@ -7630,7 +7630,7 @@
         <v>-0.718792</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.661822</v>
+        <v>-1.688561</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>-0.409053</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.56012</v>
+        <v>-1.794246</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-1.349264</v>
@@ -7671,7 +7671,7 @@
         <v>-2.300226</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.665466</v>
+        <v>-1.680753</v>
       </c>
     </row>
   </sheetData>
@@ -8436,10 +8436,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L9" s="5" t="n">
+        <v>0.522971</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.17134</v>
@@ -10465,10 +10463,8 @@
       <c r="K32" s="5" t="n">
         <v>16.916508</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L32" s="5" t="n">
+        <v>17.360803</v>
       </c>
       <c r="M32" s="5" t="n">
         <v>17.499477</v>
@@ -10625,10 +10621,8 @@
       <c r="K34" s="5" t="n">
         <v>-0.171516</v>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L34" s="5" t="n">
+        <v>0.184707</v>
       </c>
       <c r="M34" s="5" t="n">
         <v>-0.361663</v>
@@ -10971,10 +10965,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L38" s="5" t="n">
+        <v>0.522971</v>
       </c>
       <c r="M38" s="5" t="n">
         <v>0.17134</v>
@@ -11052,15 +11044,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L39" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -11141,10 +11129,8 @@
       <c r="K40" s="5" t="n">
         <v>0.001143</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L40" s="5" t="n">
+        <v>0.009906999999999999</v>
       </c>
       <c r="M40" s="5" t="n">
         <v>0.01218</v>
@@ -11416,10 +11402,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L43" s="5" t="n">
+        <v>18.396509</v>
       </c>
       <c r="M43" s="5" t="n">
         <v>19.274667</v>
@@ -17114,7 +17098,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -23712,7 +23700,11 @@
           <t>GST receivables</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -24523,7 +24515,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -25338,7 +25334,11 @@
           <t>GST Receivable</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -25706,7 +25706,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -26618,7 +26622,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -26893,7 +26901,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -29973,7 +29985,11 @@
           <t>Disposition (acquisition) of equipment</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
